--- a/sources/table_normalization/xlsx/environment-table23.xlsx
+++ b/sources/table_normalization/xlsx/environment-table23.xlsx
@@ -511,7 +511,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
@@ -521,7 +520,6 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -537,6 +535,8 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -844,7 +844,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2021,15 +2021,15 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="54" t="s">
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="52" t="s">
         <v>2</v>
       </c>
     </row>
@@ -2037,24 +2037,24 @@
       <c r="A3" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="50" t="s">
+      <c r="B3" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="52"/>
-      <c r="I3" s="55" t="s">
+      <c r="C3" s="50"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="J3" s="56" t="s">
+      <c r="J3" s="54" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:21" ht="84" customHeight="1">
-      <c r="A4" s="49"/>
+      <c r="A4" s="58"/>
       <c r="B4" s="4" t="s">
         <v>7</v>
       </c>
@@ -2076,8 +2076,8 @@
       <c r="H4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="I4" s="57"/>
-      <c r="J4" s="58"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="56"/>
     </row>
     <row r="5" spans="1:21" s="10" customFormat="1" ht="33" customHeight="1">
       <c r="A5" s="5" t="s">
